--- a/data/media/Defined_medium.xlsx
+++ b/data/media/Defined_medium.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samuel.ayensu\Desktop\ANLS_paper_PLOS_Comp\ANLS_paper\ecMMU1868-TPS\data\media\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21CD4166-D622-4A14-ABB1-E94230F6A7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7FDB845-BBB8-46C7-8994-6A75F8710B51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7230" yWindow="0" windowWidth="27015" windowHeight="20985" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Defined Medium" sheetId="2" r:id="rId1"/>
@@ -57,9 +57,6 @@
     <t>Default Medium Composition for Model Simulations</t>
   </si>
   <si>
-    <t>EAA uptake bounds determined by FVA at 99% optimal growth (×1.05 buffer). Glucose uptake: 10 mmol/gDW/h × 6C = 60 C-mmol/gDW/h.</t>
-  </si>
-  <si>
     <t>Exchange Reaction ID</t>
   </si>
   <si>
@@ -72,14 +69,6 @@
     <t>Category</t>
   </si>
   <si>
-    <t>Lower Bound
-(mmol/gDW/h)</t>
-  </si>
-  <si>
-    <t>Upper Bound
-(mmol/gDW/h)</t>
-  </si>
-  <si>
     <t>Carbon Atoms</t>
   </si>
   <si>
@@ -92,9 +81,6 @@
     <t>Water</t>
   </si>
   <si>
-    <t>H2O</t>
-  </si>
-  <si>
     <t>Solvent</t>
   </si>
   <si>
@@ -110,9 +96,6 @@
     <t>Proton</t>
   </si>
   <si>
-    <t>H+</t>
-  </si>
-  <si>
     <t>Charge balance</t>
   </si>
   <si>
@@ -122,9 +105,6 @@
     <t>Sodium</t>
   </si>
   <si>
-    <t>Na+</t>
-  </si>
-  <si>
     <t>Major ion</t>
   </si>
   <si>
@@ -134,36 +114,24 @@
     <t>Potassium</t>
   </si>
   <si>
-    <t>K+</t>
-  </si>
-  <si>
     <t>EX_cl_e</t>
   </si>
   <si>
     <t>Chloride</t>
   </si>
   <si>
-    <t>Cl-</t>
-  </si>
-  <si>
     <t>EX_ca2_e</t>
   </si>
   <si>
     <t>Calcium</t>
   </si>
   <si>
-    <t>Ca2+</t>
-  </si>
-  <si>
     <t>EX_nh4_e</t>
   </si>
   <si>
     <t>Ammonium</t>
   </si>
   <si>
-    <t>NH4+</t>
-  </si>
-  <si>
     <t>Inorganic nutrient</t>
   </si>
   <si>
@@ -185,18 +153,12 @@
     <t>Sulfate</t>
   </si>
   <si>
-    <t>SO4^2-</t>
-  </si>
-  <si>
     <t>EX_o2_e</t>
   </si>
   <si>
     <t>Oxygen</t>
   </si>
   <si>
-    <t>O2</t>
-  </si>
-  <si>
     <t>Respiratory gas</t>
   </si>
   <si>
@@ -206,9 +168,6 @@
     <t>Carbon dioxide</t>
   </si>
   <si>
-    <t>CO2</t>
-  </si>
-  <si>
     <t>Closed (secretion only)</t>
   </si>
   <si>
@@ -218,9 +177,6 @@
     <t>D-Glucose</t>
   </si>
   <si>
-    <t>C6H12O6</t>
-  </si>
-  <si>
     <t>Primary carbon source</t>
   </si>
   <si>
@@ -233,123 +189,66 @@
     <t>L-Histidine</t>
   </si>
   <si>
-    <t>C6H9N3O2</t>
-  </si>
-  <si>
     <t>Essential amino acid</t>
   </si>
   <si>
-    <t>FVA: 6C × 0.041 = 0.248 C-mmol/gDW/h</t>
-  </si>
-  <si>
     <t>EX_ile__L_e</t>
   </si>
   <si>
     <t>L-Isoleucine</t>
   </si>
   <si>
-    <t>C6H13NO2</t>
-  </si>
-  <si>
-    <t>FVA: 6C × 0.094 = 0.561 C-mmol/gDW/h</t>
-  </si>
-  <si>
     <t>EX_leu__L_e</t>
   </si>
   <si>
     <t>L-Leucine</t>
   </si>
   <si>
-    <t>FVA: 6C × 0.178 = 1.070 C-mmol/gDW/h</t>
-  </si>
-  <si>
     <t>EX_lys__L_e</t>
   </si>
   <si>
     <t>L-Lysine</t>
   </si>
   <si>
-    <t>C6H14N2O2</t>
-  </si>
-  <si>
-    <t>FVA: 6C × 0.194 = 1.161 C-mmol/gDW/h</t>
-  </si>
-  <si>
     <t>EX_met__L_e</t>
   </si>
   <si>
     <t>L-Methionine</t>
   </si>
   <si>
-    <t>C5H11NO2S</t>
-  </si>
-  <si>
-    <t>FVA: 5C × 0.065 = 0.326 C-mmol/gDW/h</t>
-  </si>
-  <si>
     <t>EX_phe__L_e</t>
   </si>
   <si>
     <t>L-Phenylalanine</t>
   </si>
   <si>
-    <t>C9H11NO2</t>
-  </si>
-  <si>
-    <t>FVA: 9C × 0.137 = 1.233 C-mmol/gDW/h</t>
-  </si>
-  <si>
     <t>EX_thr__L_e</t>
   </si>
   <si>
     <t>L-Threonine</t>
   </si>
   <si>
-    <t>C4H9NO3</t>
-  </si>
-  <si>
-    <t>FVA: 4C × 0.102 = 0.409 C-mmol/gDW/h</t>
-  </si>
-  <si>
     <t>EX_trp__L_e</t>
   </si>
   <si>
     <t>L-Tryptophan</t>
   </si>
   <si>
-    <t>C11H12N2O2</t>
-  </si>
-  <si>
-    <t>FVA: 11C × 0.004 = 0.048 C-mmol/gDW/h</t>
-  </si>
-  <si>
     <t>EX_val__L_e</t>
   </si>
   <si>
     <t>L-Valine</t>
   </si>
   <si>
-    <t>C5H11NO2</t>
-  </si>
-  <si>
-    <t>FVA: 5C × 0.115 = 0.576 C-mmol/gDW/h</t>
-  </si>
-  <si>
     <t>Summary</t>
   </si>
   <si>
     <t>Total glucose carbon capacity:</t>
   </si>
   <si>
-    <t>60 C-mmol/gDW/h (10 mmol × 6C)</t>
-  </si>
-  <si>
     <t>Total EAA carbon input:</t>
   </si>
   <si>
-    <t>5.63 C-mmol/gDW/h (9.4% of glucose carbon)</t>
-  </si>
-  <si>
     <t>EAA constraint method:</t>
   </si>
   <si>
@@ -365,9 +264,6 @@
     <t>0.327 h⁻¹</t>
   </si>
   <si>
-    <t>D-Glucose was used as the primary carbon source at 10 mmol/gDW/h.</t>
-  </si>
-  <si>
     <t>Nine EAAs (Phe, Met, Lys, Leu, His, Ile, Val, Thr, Trp) in the medium was determined by FVA at 99% optimal growth with a 1.05 buffer. Their omission abolished growth in single-nutrient omission tests, confirming essentiality.</t>
   </si>
   <si>
@@ -403,13 +299,1217 @@
   </si>
   <si>
     <t>This defined minimal medium was designed to approximate brain interstitial fluid under glucose-fed conditions and to support a physiologically realistic astrocyte growth rate for model validation and simulation.</t>
+  </si>
+  <si>
+    <r>
+      <t>SO4</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2-</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>O</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Na</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>K</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cl</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Ca</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>NH</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>13</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>14</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>S</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>9</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>12</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>N</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>O</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>H</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>11</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>NO</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FVA: 6C × 0.041 = 0.248 C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>60 C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (10 mmol × 6C)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5.63 C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (9.4% of glucose carbon)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FVA: 5C × 0.115 = 0.576 C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FVA: 11C × 0.004 = 0.048 C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FVA: 4C × 0.102 = 0.409 C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FVA: 9C × 0.137 = 1.233 C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FVA: 5C × 0.065 = 0.326 C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FVA: 6C × 0.194 = 1.161 C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FVA: 6C × 0.178 = 1.070 C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>FVA: 6C × 0.094 = 0.561 C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Lower Bound
+(C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Upper Bound
+(C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>EAA uptake bounds determined by FVA at 99% optimal growth (×1.05 buffer). Glucose uptake: 10 C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> × 6C = 60 C-C-mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>D-Glucose was used as the primary carbon source at 10 mmol.gDW</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.h</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -444,6 +1544,20 @@
     <font>
       <vertAlign val="superscript"/>
       <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -502,15 +1616,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -520,9 +1627,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -831,37 +1945,37 @@
     <col min="1" max="1" width="16.140625" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" customWidth="1"/>
     <col min="3" max="3" width="16.85546875" customWidth="1"/>
-    <col min="4" max="4" width="16.5703125" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" customWidth="1"/>
+    <col min="4" max="5" width="22.140625" customWidth="1"/>
+    <col min="6" max="6" width="22.7109375" customWidth="1"/>
     <col min="8" max="8" width="42.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
     </row>
     <row r="2" spans="1:11">
-      <c r="A2" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
+      <c r="A2" s="14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -880,638 +1994,638 @@
       <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" ht="60" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>12</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>15</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
     </row>
-    <row r="5" spans="1:11">
-      <c r="A5" s="8" t="s">
+    <row r="5" spans="1:11" ht="18.75">
+      <c r="A5" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="6">
+        <v>-1000</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1000</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="H5" s="5" t="s">
         <v>17</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="9">
-        <v>-1000</v>
-      </c>
-      <c r="F5" s="9">
-        <v>1000</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="8" t="s">
-        <v>21</v>
       </c>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
     </row>
-    <row r="6" spans="1:11">
-      <c r="A6" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="9">
+    <row r="6" spans="1:11" ht="17.25">
+      <c r="A6" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="E6" s="6">
         <v>-1000</v>
       </c>
-      <c r="F6" s="9">
+      <c r="F6" s="6">
         <v>1000</v>
       </c>
-      <c r="G6" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>21</v>
+      <c r="G6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
     </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="9">
+    <row r="7" spans="1:11" ht="17.25">
+      <c r="A7" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E7" s="6">
         <v>-1000</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="6">
         <v>1000</v>
       </c>
-      <c r="G7" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="8" t="s">
-        <v>21</v>
+      <c r="G7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="I7" s="2"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
     </row>
-    <row r="8" spans="1:11">
-      <c r="A8" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="9">
+    <row r="8" spans="1:11" ht="17.25">
+      <c r="A8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E8" s="6">
         <v>-1000</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="6">
         <v>1000</v>
       </c>
-      <c r="G8" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="8" t="s">
-        <v>21</v>
+      <c r="G8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="I8" s="2"/>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
     </row>
-    <row r="9" spans="1:11">
-      <c r="A9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="9">
+    <row r="9" spans="1:11" ht="17.25">
+      <c r="A9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="6">
         <v>-1000</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="6">
         <v>1000</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="8" t="s">
-        <v>21</v>
+      <c r="G9" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
     </row>
-    <row r="10" spans="1:11">
-      <c r="A10" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D10" s="8" t="s">
+    <row r="10" spans="1:11" ht="17.25">
+      <c r="A10" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="9">
+      <c r="C10" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="6">
         <v>-1000</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="6">
         <v>1000</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H10" s="8" t="s">
-        <v>21</v>
+      <c r="G10" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>17</v>
       </c>
       <c r="I10" s="2"/>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
     </row>
-    <row r="11" spans="1:11">
-      <c r="A11" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="9">
+    <row r="11" spans="1:11" ht="17.25">
+      <c r="A11" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="6">
         <v>-10</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="6">
         <v>1000</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>43</v>
+      <c r="G11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="8" t="s">
-        <v>44</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E12" s="9">
+      <c r="A12" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E12" s="6">
         <v>-10</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="6">
         <v>1000</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H12" s="8" t="s">
-        <v>43</v>
+      <c r="G12" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
     </row>
-    <row r="13" spans="1:11">
-      <c r="A13" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="9">
+    <row r="13" spans="1:11" ht="17.25">
+      <c r="A13" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E13" s="6">
         <v>-10</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="6">
         <v>1000</v>
       </c>
-      <c r="G13" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H13" s="8" t="s">
-        <v>43</v>
+      <c r="G13" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
     </row>
-    <row r="14" spans="1:11">
-      <c r="A14" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="9">
+    <row r="14" spans="1:11" ht="18.75">
+      <c r="A14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="6">
         <v>-10</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="6">
         <v>1000</v>
       </c>
-      <c r="G14" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="8" t="s">
-        <v>43</v>
+      <c r="G14" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
     </row>
-    <row r="15" spans="1:11">
-      <c r="A15" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="B15" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="E15" s="9">
+    <row r="15" spans="1:11" ht="18.75">
+      <c r="A15" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E15" s="6">
         <v>0</v>
       </c>
-      <c r="F15" s="9">
+      <c r="F15" s="6">
         <v>1000</v>
       </c>
-      <c r="G15" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="8" t="s">
-        <v>57</v>
+      <c r="G15" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>44</v>
       </c>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
     </row>
-    <row r="16" spans="1:11">
-      <c r="A16" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="9">
+    <row r="16" spans="1:11" ht="18.75">
+      <c r="A16" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="E16" s="6">
         <v>-10</v>
       </c>
-      <c r="F16" s="9">
+      <c r="F16" s="6">
         <v>1000</v>
       </c>
-      <c r="G16" s="9">
+      <c r="G16" s="6">
         <v>6</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>43</v>
+      <c r="H16" s="5" t="s">
+        <v>33</v>
       </c>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
     </row>
-    <row r="17" spans="1:11">
-      <c r="A17" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C17" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E17" s="11">
+    <row r="17" spans="1:11" ht="18.75">
+      <c r="A17" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E17" s="8">
         <v>-4.1321999999999998E-2</v>
       </c>
-      <c r="F17" s="11">
+      <c r="F17" s="8">
         <v>1000</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="8">
         <v>6</v>
       </c>
-      <c r="H17" s="10" t="s">
-        <v>67</v>
+      <c r="H17" s="7" t="s">
+        <v>101</v>
       </c>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
     </row>
-    <row r="18" spans="1:11">
-      <c r="A18" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C18" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E18" s="11">
+    <row r="18" spans="1:11" ht="18.75">
+      <c r="A18" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E18" s="8">
         <v>-9.3519000000000005E-2</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="8">
         <v>1000</v>
       </c>
-      <c r="G18" s="11">
+      <c r="G18" s="8">
         <v>6</v>
       </c>
-      <c r="H18" s="10" t="s">
-        <v>71</v>
+      <c r="H18" s="7" t="s">
+        <v>111</v>
       </c>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
     </row>
-    <row r="19" spans="1:11">
-      <c r="A19" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19" s="11">
+    <row r="19" spans="1:11" ht="18.75">
+      <c r="A19" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="8">
         <v>-0.178338</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="8">
         <v>1000</v>
       </c>
-      <c r="G19" s="11">
+      <c r="G19" s="8">
         <v>6</v>
       </c>
-      <c r="H19" s="10" t="s">
-        <v>74</v>
+      <c r="H19" s="7" t="s">
+        <v>110</v>
       </c>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
     </row>
-    <row r="20" spans="1:11">
-      <c r="A20" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E20" s="11">
+    <row r="20" spans="1:11" ht="18.75">
+      <c r="A20" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E20" s="8">
         <v>-0.19356200000000001</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="8">
         <v>1000</v>
       </c>
-      <c r="G20" s="11">
+      <c r="G20" s="8">
         <v>6</v>
       </c>
-      <c r="H20" s="10" t="s">
-        <v>78</v>
+      <c r="H20" s="7" t="s">
+        <v>109</v>
       </c>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
     </row>
-    <row r="21" spans="1:11">
-      <c r="A21" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E21" s="11">
+    <row r="21" spans="1:11" ht="18.75">
+      <c r="A21" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="8">
         <v>-6.5245999999999998E-2</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="8">
         <v>1000</v>
       </c>
-      <c r="G21" s="11">
+      <c r="G21" s="8">
         <v>5</v>
       </c>
-      <c r="H21" s="10" t="s">
-        <v>82</v>
+      <c r="H21" s="7" t="s">
+        <v>108</v>
       </c>
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
     </row>
-    <row r="22" spans="1:11">
-      <c r="A22" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D22" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22" s="11">
+    <row r="22" spans="1:11" ht="18.75">
+      <c r="A22" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="8">
         <v>-0.137016</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="8">
         <v>1000</v>
       </c>
-      <c r="G22" s="11">
+      <c r="G22" s="8">
         <v>9</v>
       </c>
-      <c r="H22" s="10" t="s">
-        <v>86</v>
+      <c r="H22" s="7" t="s">
+        <v>107</v>
       </c>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
     </row>
-    <row r="23" spans="1:11">
-      <c r="A23" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E23" s="11">
+    <row r="23" spans="1:11" ht="18.75">
+      <c r="A23" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E23" s="8">
         <v>-0.102218</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="8">
         <v>1000</v>
       </c>
-      <c r="G23" s="11">
+      <c r="G23" s="8">
         <v>4</v>
       </c>
-      <c r="H23" s="10" t="s">
-        <v>90</v>
+      <c r="H23" s="7" t="s">
+        <v>106</v>
       </c>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
     </row>
-    <row r="24" spans="1:11">
-      <c r="A24" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="E24" s="11">
+    <row r="24" spans="1:11" ht="18.75">
+      <c r="A24" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="8">
         <v>-4.3499999999999997E-3</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="8">
         <v>1000</v>
       </c>
-      <c r="G24" s="11">
+      <c r="G24" s="8">
         <v>11</v>
       </c>
-      <c r="H24" s="10" t="s">
-        <v>94</v>
+      <c r="H24" s="7" t="s">
+        <v>105</v>
       </c>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
     </row>
-    <row r="25" spans="1:11">
-      <c r="A25" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="D25" s="10" t="s">
+    <row r="25" spans="1:11" ht="18.75">
+      <c r="A25" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="E25" s="11">
+      <c r="B25" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E25" s="8">
         <v>-0.11526699999999999</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="8">
         <v>1000</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="8">
         <v>5</v>
       </c>
-      <c r="H25" s="10" t="s">
-        <v>98</v>
+      <c r="H25" s="7" t="s">
+        <v>104</v>
       </c>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
@@ -1532,7 +2646,7 @@
     </row>
     <row r="27" spans="1:11" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -1545,15 +2659,15 @@
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" ht="17.25">
       <c r="A28" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
+        <v>69</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="2"/>
@@ -1562,15 +2676,15 @@
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:11" ht="17.25">
       <c r="A29" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B29" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B29" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="C29" s="4"/>
-      <c r="D29" s="4"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
@@ -1581,13 +2695,13 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="C30" s="4"/>
-      <c r="D30" s="4"/>
+        <v>71</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="2"/>
@@ -1598,13 +2712,13 @@
     </row>
     <row r="31" spans="1:11">
       <c r="A31" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
+        <v>73</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="2"/>
@@ -1615,13 +2729,13 @@
     </row>
     <row r="32" spans="1:11">
       <c r="A32" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>108</v>
-      </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
+        <v>74</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -1680,11 +2794,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="36.75" customHeight="1">
-      <c r="A1" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="14" t="s">
-        <v>114</v>
+      <c r="A1" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="43.5">
@@ -1692,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="45.75">
@@ -1700,7 +2814,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="63.75" customHeight="1">
@@ -1708,7 +2822,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="26.25" customHeight="1">
@@ -1716,7 +2830,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="45.75" customHeight="1">
@@ -1724,7 +2838,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="48.75" customHeight="1">
@@ -1732,7 +2846,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
